--- a/excel/actuarial_add_in.xlsx
+++ b/excel/actuarial_add_in.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matth\actuarial_dump_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DECFAE-8E63-4177-93E7-46E6397C26FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB62A974-589C-4C64-B6B3-E2F7851D7F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14169,7 +14169,7 @@
       </c>
       <c r="B3" t="str">
         <f>_xll.ACT_VERSION()</f>
-        <v>0.7.1</v>
+        <v>0.7.2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="B8" t="str">
         <f>_xll.ACT_VERSION()</f>
-        <v>0.7.1</v>
+        <v>0.7.2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="B11">
         <f>_xll.ACT_COMMIT_COUNT()</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="B12" t="str">
         <f>_xll.ACT_COMMIT_INFO(1, "message")</f>
-        <v>Patch: replace `int? seed = null` with `object seed = null` + ResolveSeed helper across 13 stochastic functions. ExcelDna 1.9.0 mis-marshals `int?` parameters from Excel even though direct C# calls work — every cell calling the affected functions returned #VALUE! pre-fix (373 cells in the dump test).</v>
+        <v>Workbook polish + Experimental retagging. Mack-SE reference column corrected; Cat Modeling EP-curve table populated; Latest Cumulative restored as a formula; Copulas sheet gains Gaussian/Clayton/Frank/Gumbel sections; Interpolation chart shows interpolated overlay; all charts switched from smooth to straight lines; array formulas promoted via Formula2 to spill correctly. `Actuarial.Aggregate`/`Reinsurance` cat-modelling and return-period functions retagged Experimental to match Copulas/Bootstrap.</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="B304" t="str">
         <f>_xll.ACT_VERSION()</f>
-        <v>0.7.1</v>
+        <v>0.7.2</v>
       </c>
       <c r="C304" t="s">
         <v>373</v>
@@ -18759,7 +18759,7 @@
       </c>
       <c r="B307">
         <f>_xll.ACT_COMMIT_COUNT()</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C307" t="s">
         <v>379</v>
@@ -18771,7 +18771,7 @@
       </c>
       <c r="B308" t="str">
         <f>_xll.ACT_COMMIT_INFO(1, "hash")</f>
-        <v>v0.7.1</v>
+        <v>v0.7.2</v>
       </c>
       <c r="C308" t="s">
         <v>381</v>
@@ -18795,7 +18795,7 @@
       </c>
       <c r="B310" t="str">
         <f>_xll.ACT_COMMIT_INFO(1, "message")</f>
-        <v>Patch: replace `int? seed = null` with `object seed = null` + ResolveSeed helper across 13 stochastic functions. ExcelDna 1.9.0 mis-marshals `int?` parameters from Excel even though direct C# calls work — every cell calling the affected functions returned #VALUE! pre-fix (373 cells in the dump test).</v>
+        <v>Workbook polish + Experimental retagging. Mack-SE reference column corrected; Cat Modeling EP-curve table populated; Latest Cumulative restored as a formula; Copulas sheet gains Gaussian/Clayton/Frank/Gumbel sections; Interpolation chart shows interpolated overlay; all charts switched from smooth to straight lines; array formulas promoted via Formula2 to spill correctly. `Actuarial.Aggregate`/`Reinsurance` cat-modelling and return-period functions retagged Experimental to match Copulas/Bootstrap.</v>
       </c>
       <c r="C310" t="s">
         <v>383</v>

--- a/excel/actuarial_add_in.xlsx
+++ b/excel/actuarial_add_in.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matth\actuarial_dump_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB62A974-589C-4C64-B6B3-E2F7851D7F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33712A84-DAB0-45A9-A490-A6A9F3D2AA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="665">
   <si>
     <t>Actuarial Add-In Version History</t>
   </si>
@@ -122,10 +122,22 @@
     <t>Message</t>
   </si>
   <si>
+    <t>d24cc31</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>Re-baseline dump artifacts against released v0.7.2 XLL</t>
+  </si>
+  <si>
+    <t>9329c6e</t>
+  </si>
+  <si>
+    <t>v0.7.2: workbook polish + Experimental retagging</t>
+  </si>
+  <si>
     <t>04378c0</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
   </si>
   <si>
     <t>Fix int? seed marshaling — was #VALUE! in Excel for 13 functions (v0.7.1)</t>
@@ -2309,7 +2321,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E1E6-4F82-8940-82B9AFDA4784}"/>
+              <c16:uniqueId val="{00000000-BCE9-416F-BBDE-197BC32B98B7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2523,7 +2535,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8D79-477F-857F-B30AB05F7459}"/>
+              <c16:uniqueId val="{00000000-EDEB-487D-BEED-E87E24C9658D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2738,7 +2750,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D827-4AEC-A5A1-D7B99668811E}"/>
+              <c16:uniqueId val="{00000000-FBC6-415C-BDB6-3F30537073DA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2953,7 +2965,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CE4F-437F-9DB5-DDC07D3DFE56}"/>
+              <c16:uniqueId val="{00000000-4043-4572-9D64-544CEA74FA9E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3168,7 +3180,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4E37-4ABA-AB5D-7DB63AEC5453}"/>
+              <c16:uniqueId val="{00000000-45FC-4A64-A991-70361D1FAE91}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3383,7 +3395,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-13C4-4BC1-BC39-46CDC9E39E09}"/>
+              <c16:uniqueId val="{00000000-69F8-4015-ACCE-31C588A96B95}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3604,7 +3616,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B958-4E2A-B00F-245DA46197FF}"/>
+              <c16:uniqueId val="{00000000-51F5-4939-A6CB-D19790820EF1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3826,7 +3838,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A8BC-4949-BE23-68CD01194A75}"/>
+              <c16:uniqueId val="{00000000-914C-49F9-A063-8C42CE80C760}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4048,7 +4060,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1D4B-4CBF-BF3F-764526ACE43A}"/>
+              <c16:uniqueId val="{00000000-95B7-47E0-8CCA-68DAED72807B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4270,7 +4282,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DCDA-41BA-AD2A-1B2E799AD107}"/>
+              <c16:uniqueId val="{00000000-AFF6-403F-8079-9B4698DD369E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4498,7 +4510,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-88DC-43F7-B7FF-35FE22A40654}"/>
+              <c16:uniqueId val="{00000000-DD54-4419-9677-F6225FD0D318}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4726,7 +4738,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3538-4B85-AA6A-7E97175DDCA3}"/>
+              <c16:uniqueId val="{00000000-12CC-4235-B90D-1E90E7C6CEF9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4947,7 +4959,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F6DE-4217-A9F1-3AD5E21EEADB}"/>
+              <c16:uniqueId val="{00000000-A299-4F8C-A921-AB2FAD92F825}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5163,7 +5175,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D390-48D8-AE7A-DCC4F5572122}"/>
+              <c16:uniqueId val="{00000000-F202-4D64-9623-8C6F339591B4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5373,7 +5385,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4CD0-47C9-84AC-19CB76037571}"/>
+              <c16:uniqueId val="{00000000-FB8F-4F36-BEA5-A90E708708D2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5595,7 +5607,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-015E-4976-9A3A-02EB31B5FEE8}"/>
+              <c16:uniqueId val="{00000000-1839-4987-A850-B79F81688B46}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5816,7 +5828,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-073F-47A1-9FBD-6ACDB41A8358}"/>
+              <c16:uniqueId val="{00000000-A1C0-44C1-987C-A777C0098E80}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6037,7 +6049,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4B35-4225-B08E-1B07DE330F8B}"/>
+              <c16:uniqueId val="{00000000-A7BF-42D9-92C3-2CE3D969D7B7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6267,7 +6279,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E3F8-475E-9FF7-AA5891D60A43}"/>
+              <c16:uniqueId val="{00000000-B3B0-48F8-BFD4-C96560F9C8BB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6375,7 +6387,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E3F8-475E-9FF7-AA5891D60A43}"/>
+              <c16:uniqueId val="{00000001-B3B0-48F8-BFD4-C96560F9C8BB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6483,7 +6495,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-E3F8-475E-9FF7-AA5891D60A43}"/>
+              <c16:uniqueId val="{00000002-B3B0-48F8-BFD4-C96560F9C8BB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6591,7 +6603,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-E3F8-475E-9FF7-AA5891D60A43}"/>
+              <c16:uniqueId val="{00000003-B3B0-48F8-BFD4-C96560F9C8BB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6699,7 +6711,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-E3F8-475E-9FF7-AA5891D60A43}"/>
+              <c16:uniqueId val="{00000004-B3B0-48F8-BFD4-C96560F9C8BB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6908,7 +6920,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3FF6-44F0-AD5F-B45A685D245D}"/>
+              <c16:uniqueId val="{00000000-A209-4777-A777-58A15D2F8D9F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6999,7 +7011,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3FF6-44F0-AD5F-B45A685D245D}"/>
+              <c16:uniqueId val="{00000001-A209-4777-A777-58A15D2F8D9F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7230,7 +7242,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C32B-462E-8E8C-67C613A6BB3F}"/>
+              <c16:uniqueId val="{00000000-85BF-429C-A235-474D68C720FD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7459,7 +7471,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8B55-4B8F-88A3-C2D7E1613381}"/>
+              <c16:uniqueId val="{00000000-2186-4CFB-9B9F-20EC86B46A2B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7563,7 +7575,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8B55-4B8F-88A3-C2D7E1613381}"/>
+              <c16:uniqueId val="{00000001-2186-4CFB-9B9F-20EC86B46A2B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7802,7 +7814,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B089-4BD5-9228-E4B3871B6FC7}"/>
+              <c16:uniqueId val="{00000000-924B-4E0B-992E-F9D401F301E6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8029,7 +8041,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4E20-4363-BA6C-5E76A0C1D660}"/>
+              <c16:uniqueId val="{00000000-1925-43CD-A689-0B00262217D5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8799,7 +8811,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E94A-4B45-BF0F-FDE51BB00CCA}"/>
+              <c16:uniqueId val="{00000000-2704-4673-81CD-9818D4374F1F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9269,7 +9281,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CFC2-4B32-B0BE-3DC3A56EA43A}"/>
+              <c16:uniqueId val="{00000000-1F87-4923-AEF6-F5C47ED3506B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9739,7 +9751,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1069-4903-B377-F9CA3972922E}"/>
+              <c16:uniqueId val="{00000000-44D8-4ADE-8BFA-534E5A64CC21}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10209,7 +10221,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5143-40C4-9AD7-9088DFF20448}"/>
+              <c16:uniqueId val="{00000000-F7C4-4222-BF62-A34B2A6C601F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10679,7 +10691,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-393D-486F-ACEE-FA655E2448A5}"/>
+              <c16:uniqueId val="{00000000-FA84-4457-9464-A02798656669}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11028,7 +11040,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E687-4D6C-90CF-98024F0519D6}"/>
+              <c16:uniqueId val="{00000000-E28D-4350-B62C-CCDEDE0992F7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11221,7 +11233,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F306-408F-B2BF-56616F1D8B75}"/>
+              <c16:uniqueId val="{00000000-50F4-49A8-A429-5C7AD67CC8FA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11442,7 +11454,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CD19-4F05-B538-5DAC0A745426}"/>
+              <c16:uniqueId val="{00000000-A8A8-41BE-8B6B-610CD77E615E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11657,7 +11669,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2CF7-4EA7-B0BF-9B793A9CB95B}"/>
+              <c16:uniqueId val="{00000000-4770-4378-9F3D-7DBF73E935BA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11872,7 +11884,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A6CA-4D4C-ACEF-A4C4DEF59E23}"/>
+              <c16:uniqueId val="{00000000-EA1B-4712-AAC5-848EF526FF64}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12087,7 +12099,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-282D-4A90-A86D-9CB8DAF4C203}"/>
+              <c16:uniqueId val="{00000000-6A41-4FFF-A880-9A256C87D81B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12314,7 +12326,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4C74-4403-85E5-BB488785FCB4}"/>
+              <c16:uniqueId val="{00000000-BC2B-49E3-B90D-127EF51EE72A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12524,7 +12536,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-48D8-4F2F-87D5-3A4DF872CF3A}"/>
+              <c16:uniqueId val="{00000000-D65B-43D9-99A8-B5E13408001D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -14149,7 +14161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -14327,32 +14339,54 @@
         <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -14375,32 +14409,32 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -14408,7 +14442,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B10">
         <v>0.5</v>
@@ -14416,7 +14450,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B11">
         <v>20</v>
@@ -14424,13 +14458,13 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -14675,17 +14709,17 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B38">
         <v>2</v>
@@ -14693,7 +14727,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B39">
         <v>40</v>
@@ -14701,16 +14735,16 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -15371,59 +15405,59 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B87" s="15">
         <f>_xll.ACT_AGGREGATE_MEAN(C42:C82, B10)</f>
         <v>1.9777759659272356</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B88" s="15">
         <f>_xll.ACT_AGGREGATE_STDEV(C42:C82, B10)</f>
         <v>2.0065233076088309</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B89" s="15">
         <f>_xll.ACT_AGGREGATE_VAR_STAT(C42:C82, B10)</f>
         <v>4.0261357839774838</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B90" s="15">
         <f>_xll.ACT_AGGREGATE_VAR(0.95, C42:C82, B10)</f>
@@ -15433,7 +15467,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B91" s="15">
         <f>_xll.ACT_AGGREGATE_TVAR(0.95, C42:C82, B10)</f>
@@ -15443,7 +15477,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B92" s="15">
         <f>_xll.ACT_AGGREGATE_CDF(3, C42:C82, B10)</f>
@@ -15453,17 +15487,17 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B97">
         <v>2</v>
@@ -15471,7 +15505,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B98">
         <v>0.5</v>
@@ -15479,16 +15513,16 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -16149,35 +16183,35 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B145" s="15">
         <f>_xll.ACT_AGGREGATE_MEAN(C101:C141, B10)</f>
         <v>1.9749200654232155</v>
       </c>
       <c r="C145" s="16" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B146" s="15">
         <f>_xll.ACT_AGGREGATE_STDEV(C101:C141, B10)</f>
@@ -16187,7 +16221,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B147" s="15">
         <f>_xll.ACT_AGGREGATE_VAR(0.95, C101:C141, B10)</f>
@@ -16197,7 +16231,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B148" s="15">
         <f>_xll.ACT_AGGREGATE_TVAR(0.95, C101:C141, B10)</f>
@@ -16224,25 +16258,25 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -16287,21 +16321,21 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -16317,7 +16351,7 @@
         <v>200000</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -16333,7 +16367,7 @@
         <v>750000</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -16349,7 +16383,7 @@
         <v>1500000</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -16365,17 +16399,17 @@
         <v>2000000</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B21" s="17">
         <f>_xll.ACT_AAL_FROM_OEP(A7:A11, B7:B11)</f>
@@ -16400,118 +16434,118 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <f>_xll.ACT_DIST_POISSON_PDF(3, 5)</f>
         <v>0.1403738958142805</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <f>_xll.ACT_DIST_POISSON_CDF(3, 5)</f>
         <v>0.26502591529736219</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B8">
         <f>_xll.ACT_DIST_POISSON_INV(0.5, 5)</f>
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B9" cm="1">
         <f t="array" ref="B9">_xll.ACT_DIST_POISSON_FIT({1,2,3,4,5,6,7})</f>
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12">
         <f>_xll.ACT_DIST_NEGBIN_PDF(5, 5, 0.3)</f>
         <v>5.1459672600000235E-2</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B13">
         <f>_xll.ACT_DIST_NEGBIN_CDF(5, 5, 0.3)</f>
         <v>0.1502683326000005</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B14">
         <f>_xll.ACT_DIST_NEGBIN_INV(0.5, 5, 0.3)</f>
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B15" cm="1">
         <f t="array" ref="B15:B16">TRANSPOSE(_xll.ACT_DIST_NEGBIN_FIT({1,2,3,4,5,6,7,8,9,10}))</f>
         <v>8.2500000000000018</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -16519,417 +16553,417 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B21">
         <f>_xll.ACT_DIST_ZTPOISSON_PDF(2, 3)</f>
         <v>0.23578063421065179</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B22">
         <f>_xll.ACT_DIST_ZTPOISSON_CDF(2, 3)</f>
         <v>0.39296772368442162</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B23">
         <f>_xll.ACT_DIST_ZTPOISSON_INV(0.5, 3)</f>
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B24">
         <f>_xll.ACT_DIST_ZTPOISSON_MEAN(3)</f>
         <v>3.1571870894737679</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B27">
         <f>_xll.ACT_DIST_ZTNEGBIN_PDF(3, 5, 0.3)</f>
         <v>2.9243211002735654E-2</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B28">
         <f>_xll.ACT_DIST_ZTNEGBIN_CDF(3, 5, 0.3)</f>
         <v>5.5672935232616183E-2</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B29">
         <f>_xll.ACT_DIST_ZTNEGBIN_INV(0.5, 5, 0.3)</f>
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B30">
         <f>_xll.ACT_DIST_ZTNEGBIN_MEAN(5, 0.3)</f>
         <v>11.695085724978366</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B33">
         <f>_xll.ACT_DIST_ZTBINOM_PDF(3, 10, 0.3)</f>
         <v>0.27458425765526495</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B34">
         <f>_xll.ACT_DIST_ZTBINOM_CDF(3, 10, 0.3)</f>
         <v>0.63942537778054698</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B35">
         <f>_xll.ACT_DIST_ZTBINOM_INV(0.5, 10, 0.3)</f>
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B36">
         <f>_xll.ACT_DIST_ZTBINOM_MEAN(10, 0.3)</f>
         <v>3.0872059262738478</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B39">
         <f>_xll.ACT_DIST_ZTGEOM_PDF(2, 0.3)</f>
         <v>0.21</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B40">
         <f>_xll.ACT_DIST_ZTGEOM_CDF(2, 0.3)</f>
         <v>0.51</v>
       </c>
       <c r="C40" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B41">
         <f>_xll.ACT_DIST_ZTGEOM_INV(0.5, 0.3)</f>
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B42">
         <f>_xll.ACT_DIST_ZTGEOM_MEAN(0.3)</f>
         <v>3.3333333333333335</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B47">
         <f>_xll.ACT_DIST_ZMPOISSON_PDF(2, 3, 0.2)</f>
         <v>0.17923344612431022</v>
       </c>
       <c r="C47" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B48">
         <f>_xll.ACT_DIST_ZMPOISSON_CDF(2, 3, 0.2)</f>
         <v>0.53855206490147634</v>
       </c>
       <c r="C48" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B49">
         <f>_xll.ACT_DIST_ZMPOISSON_INV(0.5, 3, 0.2)</f>
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B50">
         <f>_xll.ACT_DIST_ZMPOISSON_MEAN(3, 0.2)</f>
         <v>2.4000000000000004</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B51">
         <f>_xll.ACT_DIST_ZMPOISSON_VAR(3, 0.2)</f>
         <v>3.8400000000000007</v>
       </c>
       <c r="C51" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B54">
         <f>_xll.ACT_DIST_ZMNEGBIN_PDF(3, 5, 0.3, 0.2)</f>
         <v>2.3337719999999205E-2</v>
       </c>
       <c r="C54" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B55">
         <f>_xll.ACT_DIST_ZMNEGBIN_CDF(3, 5, 0.3, 0.2)</f>
         <v>0.24637412000000075</v>
       </c>
       <c r="C55" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B56">
         <f>_xll.ACT_DIST_ZMNEGBIN_INV(0.5, 5, 0.3, 0.2)</f>
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B57">
         <f>_xll.ACT_DIST_ZMNEGBIN_MEAN(5, 0.3, 0.2)</f>
         <v>9.3333333333333339</v>
       </c>
       <c r="C57" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B58">
         <f>_xll.ACT_DIST_ZMNEGBIN_VAR(5, 0.3, 0.2)</f>
         <v>52.888888888888893</v>
       </c>
       <c r="C58" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B63">
         <f>_xll.ACT_DIST_LOGNORM_PDF(1, 0, 1)</f>
         <v>0.39894228040143265</v>
       </c>
       <c r="C63" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B64">
         <f>_xll.ACT_DIST_LOGNORM_CDF(1, 0, 1)</f>
         <v>0.5</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B65">
         <f>_xll.ACT_DIST_LOGNORM_INV(0.5, 0, 1)</f>
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B66" cm="1">
         <f t="array" ref="B66:B67">TRANSPOSE(_xll.ACT_DIST_LOGNORM_FIT({1,2,3,4,5}))</f>
         <v>0.95749834855640914</v>
       </c>
       <c r="C66" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -16937,60 +16971,60 @@
         <v>0.63550943874630406</v>
       </c>
       <c r="C67" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B70">
         <f>_xll.ACT_DIST_GAMMA_PDF(1, 2, 1)</f>
         <v>0.36787944117144233</v>
       </c>
       <c r="C70" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B71">
         <f>_xll.ACT_DIST_GAMMA_CDF(1, 2, 1)</f>
         <v>0.26424111765711528</v>
       </c>
       <c r="C71" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B72">
         <f>_xll.ACT_DIST_GAMMA_INV(0.5, 2, 1)</f>
         <v>1.6783469900166605</v>
       </c>
       <c r="C72" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B73" cm="1">
         <f t="array" ref="B73:B74">TRANSPOSE(_xll.ACT_DIST_GAMMA_FIT({1,2,3,4,5}))</f>
         <v>3.5999999999999996</v>
       </c>
       <c r="C73" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -16998,60 +17032,60 @@
         <v>1.2</v>
       </c>
       <c r="C74" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B77">
         <f>_xll.ACT_DIST_PARETO_PDF(2, 2, 1)</f>
         <v>0.25</v>
       </c>
       <c r="C77" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B78">
         <f>_xll.ACT_DIST_PARETO_CDF(2, 2, 1)</f>
         <v>0.75</v>
       </c>
       <c r="C78" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B79">
         <f>_xll.ACT_DIST_PARETO_INV(0.5, 2, 1)</f>
         <v>1.4142135623730951</v>
       </c>
       <c r="C79" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B80" cm="1">
         <f t="array" ref="B80:B81">TRANSPOSE(_xll.ACT_DIST_PARETO_FIT({1.5,2,2.5,3,4,5}, 1))</f>
         <v>0.98211766976467296</v>
       </c>
       <c r="C80" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -17059,60 +17093,60 @@
         <v>1</v>
       </c>
       <c r="C81" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B84">
         <f>_xll.ACT_DIST_WEIBULL_PDF(0.5, 2, 1)</f>
         <v>0.77880078307140488</v>
       </c>
       <c r="C84" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B85">
         <f>_xll.ACT_DIST_WEIBULL_CDF(0.5, 2, 1)</f>
         <v>0.22119921692859512</v>
       </c>
       <c r="C85" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B86">
         <f>_xll.ACT_DIST_WEIBULL_INV(0.5, 2, 1)</f>
         <v>0.83255461115769769</v>
       </c>
       <c r="C86" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B87" cm="1">
         <f t="array" ref="B87:B88">TRANSPOSE(_xll.ACT_DIST_WEIBULL_FIT({0.5,1,1.5,2,2.5}))</f>
         <v>1.9817850145759779</v>
       </c>
       <c r="C87" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -17120,60 +17154,60 @@
         <v>1.6922682595881258</v>
       </c>
       <c r="C88" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B91">
         <f>_xll.ACT_DIST_BETA_PDF(0.3, 2, 5)</f>
         <v>2.1608999999999954</v>
       </c>
       <c r="C91" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B92">
         <f>_xll.ACT_DIST_BETA_CDF(0.3, 2, 5)</f>
         <v>0.57982499999999859</v>
       </c>
       <c r="C92" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B93">
         <f>_xll.ACT_DIST_BETA_INV(0.5, 2, 5)</f>
         <v>0.26444998329566033</v>
       </c>
       <c r="C93" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B94" cm="1">
         <f t="array" ref="B94:B95">TRANSPOSE(_xll.ACT_DIST_BETA_FIT({0.1,0.2,0.3,0.4}))</f>
         <v>2.5625</v>
       </c>
       <c r="C94" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -17181,113 +17215,113 @@
         <v>7.6875</v>
       </c>
       <c r="C95" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B98">
         <f>_xll.ACT_DIST_EXP_PDF(1, 0.5)</f>
         <v>0.30326532985631671</v>
       </c>
       <c r="C98" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B99">
         <f>_xll.ACT_DIST_EXP_CDF(1, 0.5)</f>
         <v>0.39346934028736658</v>
       </c>
       <c r="C99" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B100">
         <f>_xll.ACT_DIST_EXP_INV(0.5, 0.5)</f>
         <v>1.3862943611198906</v>
       </c>
       <c r="C100" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B101" cm="1">
         <f t="array" ref="B101">_xll.ACT_DIST_EXP_FIT({1,2,3,4,5})</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C101" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B104">
         <f>_xll.ACT_DIST_GPD_PDF(1, 0.5, 1)</f>
         <v>0.29629629629629628</v>
       </c>
       <c r="C104" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B105">
         <f>_xll.ACT_DIST_GPD_CDF(1, 0.5, 1)</f>
         <v>0.55555555555555558</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B106">
         <f>_xll.ACT_DIST_GPD_INV(0.5, 0.5, 1)</f>
         <v>0.82842712474619029</v>
       </c>
       <c r="C106" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B107" cm="1">
         <f t="array" ref="B107:B108">TRANSPOSE(_xll.ACT_DIST_GPD_FIT({1,2,3,4,5,6,7,8,9,10,12,15}))</f>
         <v>-0.79069767441860339</v>
       </c>
       <c r="C107" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -17295,60 +17329,60 @@
         <v>12.236434108527124</v>
       </c>
       <c r="C108" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B111">
         <f>_xll.ACT_DIST_BURR_PDF(1, 2, 3, 1)</f>
         <v>0.375</v>
       </c>
       <c r="C111" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B112">
         <f>_xll.ACT_DIST_BURR_CDF(1, 2, 3, 1)</f>
         <v>0.875</v>
       </c>
       <c r="C112" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B113">
         <f>_xll.ACT_DIST_BURR_INV(0.5, 2, 3, 1)</f>
         <v>0.50982452853395865</v>
       </c>
       <c r="C113" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B114" cm="1">
         <f t="array" ref="B114:B116">TRANSPOSE(_xll.ACT_DIST_BURR_FIT({0.5,1,1.5,2,3}))</f>
         <v>3</v>
       </c>
       <c r="C114" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -17356,7 +17390,7 @@
         <v>3</v>
       </c>
       <c r="C115" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -17364,1463 +17398,1463 @@
         <v>2.3817408282221408</v>
       </c>
       <c r="C116" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B119">
         <f>_xll.ACT_DIST_NORMAL_PDF(0, 0, 1)</f>
         <v>0.39894228040143265</v>
       </c>
       <c r="C119" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B120">
         <f>_xll.ACT_DIST_NORMAL_CDF(0, 0, 1)</f>
         <v>0.5</v>
       </c>
       <c r="C120" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B121">
         <f>_xll.ACT_DIST_NORMAL_INV(0.975, 0, 1)</f>
         <v>1.9599639845400538</v>
       </c>
       <c r="C121" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B124">
         <f>_xll.ACT_DIST_INVGAUSS_PDF(1, 1, 2)</f>
         <v>0.56418958354775628</v>
       </c>
       <c r="C124" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B125">
         <f>_xll.ACT_DIST_INVGAUSS_CDF(1, 1, 2)</f>
         <v>0.62769783815525282</v>
       </c>
       <c r="C125" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B126">
         <f>_xll.ACT_DIST_INVGAUSS_INV(0.5, 1, 2)</f>
         <v>0.80433904129600164</v>
       </c>
       <c r="C126" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B129">
         <f>_xll.ACT_DIST_LOGLOGISTIC_PDF(1, 2, 1)</f>
         <v>0.22222222222222221</v>
       </c>
       <c r="C129" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B130">
         <f>_xll.ACT_DIST_LOGLOGISTIC_CDF(1, 2, 1)</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C130" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B131">
         <f>_xll.ACT_DIST_LOGLOGISTIC_INV(0.5, 2, 1)</f>
         <v>2</v>
       </c>
       <c r="C131" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B134">
         <f>_xll.ACT_DIST_LOMAX_PDF(1, 2, 1)</f>
         <v>0.25</v>
       </c>
       <c r="C134" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B135">
         <f>_xll.ACT_DIST_LOMAX_CDF(1, 2, 1)</f>
         <v>0.75</v>
       </c>
       <c r="C135" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B136">
         <f>_xll.ACT_DIST_LOMAX_INV(0.5, 2, 1)</f>
         <v>0.41421356237309515</v>
       </c>
       <c r="C136" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B139">
         <f>_xll.ACT_DIST_PARETO3_PDF(1, 0, 1, 2)</f>
         <v>0.25</v>
       </c>
       <c r="C139" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B140">
         <f>_xll.ACT_DIST_PARETO3_CDF(1, 0, 1, 2)</f>
         <v>0.75</v>
       </c>
       <c r="C140" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B141">
         <f>_xll.ACT_DIST_PARETO3_INV(0.5, 0, 1, 2)</f>
         <v>0.41421356237309515</v>
       </c>
       <c r="C141" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B142">
         <f>_xll.ACT_DIST_PARETO3_MEAN(0, 1, 2)</f>
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B145">
         <f>_xll.ACT_DIST_PARETO4_PDF(1, 0, 1, 2, 3)</f>
         <v>9.375E-2</v>
       </c>
       <c r="C145" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B146">
         <f>_xll.ACT_DIST_PARETO4_CDF(1, 0, 1, 2, 3)</f>
         <v>0.875</v>
       </c>
       <c r="C146" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B147">
         <f>_xll.ACT_DIST_PARETO4_INV(0.5, 0, 1, 2, 3)</f>
         <v>6.755895217845316E-2</v>
       </c>
       <c r="C147" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B150">
         <f>_xll.ACT_DIST_LNPARETO_PDF(5, 0, 1, 10)</f>
         <v>2.18507148303272E-2</v>
       </c>
       <c r="C150" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B151">
         <f>_xll.ACT_DIST_LNPARETO_CDF(5, 0, 1, 10)</f>
         <v>0.94623968954833682</v>
       </c>
       <c r="C151" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B152">
         <f>_xll.ACT_DIST_LNPARETO_ALPHA(0, 1, 10)</f>
         <v>2.6437664318162253</v>
       </c>
       <c r="C152" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B153">
         <f>_xll.ACT_DIST_EXPPARETO_PDF(5, 0.5, 10)</f>
         <v>4.10424993119494E-2</v>
       </c>
       <c r="C153" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B154">
         <f>_xll.ACT_DIST_EXPPARETO_CDF(5, 0.5, 10)</f>
         <v>0.91791500137610116</v>
       </c>
       <c r="C154" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B155">
         <f>_xll.ACT_DIST_EXPPARETO_ALPHA(0.5, 10)</f>
         <v>5</v>
       </c>
       <c r="C155" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B156">
         <f>_xll.ACT_DIST_POWPARETO_PDF(5, 2, 0.5, 10)</f>
         <v>5.656854249492381E-2</v>
       </c>
       <c r="C156" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B157">
         <f>_xll.ACT_DIST_POWPARETO_CDF(5, 2, 0.5, 10)</f>
         <v>0.56568542494923812</v>
       </c>
       <c r="C157" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B162">
         <f>_xll.ACT_DIST_POISSON_LEV(5, 5)</f>
         <v>4.1226631511607437</v>
       </c>
       <c r="C162" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B165">
         <f>_xll.ACT_DIST_NEGBIN_LEV(10, 5, 0.3)</f>
         <v>8.4026604565508922</v>
       </c>
       <c r="C165" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B168">
         <f>_xll.ACT_DIST_EXP_LEV(2, 0.5)</f>
         <v>1.2642411176571153</v>
       </c>
       <c r="C168" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B171">
         <f>_xll.ACT_DIST_LOGNORM_LEV(2, 0, 1)</f>
         <v>1.1138701491642353</v>
       </c>
       <c r="C171" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B174">
         <f>_xll.ACT_DIST_GAMMA_LEV(2, 2, 1)</f>
         <v>1.4586588670535474</v>
       </c>
       <c r="C174" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B177">
         <f>_xll.ACT_DIST_PARETO_LEV(2, 2, 1)</f>
         <v>1.5</v>
       </c>
       <c r="C177" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B180">
         <f>_xll.ACT_DIST_LOMAX_LEV(2, 2, 1)</f>
         <v>0.66666666666666674</v>
       </c>
       <c r="C180" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B183">
         <f>_xll.ACT_DIST_GPD_LEV(2, 0.5, 1)</f>
         <v>1</v>
       </c>
       <c r="C183" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B186">
         <f>_xll.ACT_DIST_WEIBULL_LEV(1, 2, 1)</f>
         <v>0.74682413281242699</v>
       </c>
       <c r="C186" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B189">
         <f>_xll.ACT_DIST_BETA_LEV(0.5, 2, 5)</f>
         <v>0.27566964285714529</v>
       </c>
       <c r="C189" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B192">
         <f>_xll.ACT_DIST_BURR_LEV(1, 2, 3, 1)</f>
         <v>0.54452431127404766</v>
       </c>
       <c r="C192" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B195">
         <f>_xll.ACT_DIST_INVGAUSS_LEV(1, 1, 2)</f>
         <v>0.74460432368948881</v>
       </c>
       <c r="C195" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B198">
         <f>_xll.ACT_DIST_LOGLOGISTIC_LEV(2, 2, 1)</f>
         <v>1.386294361119951</v>
       </c>
       <c r="C198" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B202">
         <f>_xll.ACT_EXPOSURE_MBBEFD(0.5, 2, 3)</f>
         <v>0.59570401563352471</v>
       </c>
       <c r="C202" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B203">
         <f>_xll.ACT_EXPOSURE_SWISSRE(0.5, 1)</f>
         <v>0.87357700106537017</v>
       </c>
       <c r="C203" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B204">
         <f>_xll.ACT_EXPOSURE_SWISSRE(0.5, 3)</f>
         <v>0.97133932405449286</v>
       </c>
       <c r="C204" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B205">
         <f>_xll.ACT_EXPOSURE_SWISSRE(0.5, 5)</f>
         <v>0.66827198771258944</v>
       </c>
       <c r="C205" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B206">
         <f>_xll.ACT_EXPOSURE_LLOYDS(0.5, 1)</f>
         <v>0.64644660940672627</v>
       </c>
       <c r="C206" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B207">
         <f>_xll.ACT_EXPOSURE_LLOYDS(0.5, 2)</f>
         <v>0.75</v>
       </c>
       <c r="C207" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B208">
         <f>_xll.ACT_EXPOSURE_LLOYDS(0.5, 3)</f>
         <v>0.875</v>
       </c>
       <c r="C208" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B209">
         <f>_xll.ACT_EXPOSURE_LLOYDS(0.5, 4)</f>
         <v>0.9375</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B210">
         <f>_xll.ACT_EXPOSURE_POWER(0.5, 2)</f>
         <v>0.25</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B211">
         <f>_xll.ACT_EXPOSURE_INVERSE_POWER(0.5, 2)</f>
         <v>0.75</v>
       </c>
       <c r="C211" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B212">
         <f>_xll.ACT_EXPOSURE_PARETO(0.5, 2)</f>
         <v>0.29289321881345243</v>
       </c>
       <c r="C212" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B213">
         <f>_xll.ACT_EXPOSURE_RIEBESELL(0.5, 0.8)</f>
         <v>0.65947934199881397</v>
       </c>
       <c r="C213" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B214">
         <f>_xll.ACT_EXPOSURE_RIEBESELL_INV(0.7, 0.8)</f>
         <v>0.53793097181669658</v>
       </c>
       <c r="C214" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B218">
         <f>_xll.ACT_XOL_LAYER_LOSS(5000000, 1000000, 4000000)</f>
         <v>4000000</v>
       </c>
       <c r="C218" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B219">
         <f>_xll.ACT_XOL_EXPECTED_LOSS(1000000, 4000000, 2, 100000, 0.1)</f>
         <v>0</v>
       </c>
       <c r="C219" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B220">
         <f>_xll.ACT_ILF_PARETO(2000000, 1000000, 2)</f>
         <v>1.000000250000125</v>
       </c>
       <c r="C220" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B221">
         <f>_xll.ACT_EXPOSURE_LAYER_RATE(0.1, 0.5, 0.05, 2, 3)</f>
         <v>2.2335159284056889E-2</v>
       </c>
       <c r="C221" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B225" t="str">
         <f>INDEX(_xll.ACT_CAT_ELT_TO_YLT({0.01,0.02,0.05,0.1}, {1000000,500000,200000,50000}, 100, 42), 1, 1)</f>
         <v>Year</v>
       </c>
       <c r="C225" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B226" t="str">
         <f>INDEX(_xll.ACT_CAT_YLT_OEP_CURVE({500000,200000,0,100000,300000}), 1, 1)</f>
         <v>Return Period</v>
       </c>
       <c r="C226" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B227" t="str">
         <f>INDEX(_xll.ACT_CAT_YLT_AEP_CURVE({500000,200000,0,100000,300000}), 1, 1)</f>
         <v>Return Period</v>
       </c>
       <c r="C227" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B228" t="str">
         <f>INDEX(_xll.ACT_CAT_OEP_CURVE_RP({500000,200000,0,100000,300000}, {5,10,25}), 1, 1)</f>
         <v>Return Period</v>
       </c>
       <c r="C228" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B229" t="str">
         <f>INDEX(_xll.ACT_CAT_AEP_CURVE_RP({500000,200000,0,100000,300000}, {5,10,25}), 1, 1)</f>
         <v>Return Period</v>
       </c>
       <c r="C229" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B233">
         <f>_xll.ACT_VAR_FROM_SAMPLES({100,200,300,400,500,600,700,800,900,1000}, 0.95)</f>
         <v>1000</v>
       </c>
       <c r="C233" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B234">
         <f>_xll.ACT_TVAR_FROM_SAMPLES({100,200,300,400,500,600,700,800,900,1000}, 0.95)</f>
         <v>1000</v>
       </c>
       <c r="C234" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B237">
         <f>_xll.ACT_RETURN_PERIOD_LOSS({100,50,25,10,5}, {1000000,2000000,3000000,5000000,10000000}, 20, "LOG")</f>
         <v>3487058.4052679399</v>
       </c>
       <c r="C237" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B238">
         <f>INDEX(_xll.ACT_RETURN_PERIOD_TABLE({100,50,25,10,5}, {1000000,2000000,3000000,5000000,10000000}, {10,25,50,100}), 1, 1)</f>
         <v>10</v>
       </c>
       <c r="C238" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B239">
         <f>_xll.ACT_AAL_FROM_OEP({100,50,25,10,5}, {1000000,2000000,3000000,5000000,10000000})</f>
         <v>3055000</v>
       </c>
       <c r="C239" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B243">
         <f>_xll.ACT_INTERP({1,2,3,4,5}, {10,20,35,55,80}, 2.5, "LINEAR")</f>
         <v>27.5</v>
       </c>
       <c r="C243" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B244">
         <f>_xll.ACT_INTERP({1,2,3,4,5}, {10,20,35,55,80}, 0.5, "FLAT")</f>
         <v>10</v>
       </c>
       <c r="C244" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B245">
         <f>_xll.ACT_INTERP({1,2,3,4,5}, {10,20,35,55,80}, 6, "GRADIENT")</f>
         <v>105</v>
       </c>
       <c r="C245" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B246">
         <f>_xll.ACT_INTERP_LOG({1,2,3,4,5}, {10,20,35,55,80}, 2.5)</f>
         <v>28.255095698198126</v>
       </c>
       <c r="C246" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B247">
         <f>_xll.ACT_INTERP2D({1,2,3}, {10,20,30}, {100,200,300;110,220,330;120,240,360}, 1.5, 15)</f>
         <v>157.5</v>
       </c>
       <c r="C247" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B251">
         <f>INDEX(_xll.ACT_COPULA_GAUSSIAN({1,0.5;0.5,1}, 5, 42), 1, 1)</f>
         <v>0.65850557510982255</v>
       </c>
       <c r="C251" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B252">
         <f>INDEX(_xll.ACT_COPULA_GAUSSIAN_SINGLE({1,0.5;0.5,1}, 42), 1, 1)</f>
         <v>0.65850557510982255</v>
       </c>
       <c r="C252" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B255">
         <f>INDEX(_xll.ACT_COPULA_STUDENT_T({1,0.5;0.5,1}, 5, 5, 42), 1, 1)</f>
         <v>0.65170123690316561</v>
       </c>
       <c r="C255" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B256">
         <f>INDEX(_xll.ACT_COPULA_STUDENT_T_SINGLE({1,0.5;0.5,1}, 5, 42), 1, 1)</f>
         <v>0.65170123690316561</v>
       </c>
       <c r="C256" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B259">
         <f>INDEX(_xll.ACT_COPULA_CLAYTON(2, 5, 42), 1, 1)</f>
         <v>0.66810646591154232</v>
       </c>
       <c r="C259" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B260">
         <f>INDEX(_xll.ACT_COPULA_CLAYTON_SINGLE(2, 42), 1, 1)</f>
         <v>0.66810646591154232</v>
       </c>
       <c r="C260" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B261">
         <f>_xll.ACT_COPULA_CLAYTON_CDF(0.5, 0.5, 2)</f>
         <v>0.37796447300922725</v>
       </c>
       <c r="C261" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B264">
         <f>INDEX(_xll.ACT_COPULA_FRANK(5, 5, 42), 1, 1)</f>
         <v>0.66810646591154232</v>
       </c>
       <c r="C264" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B265">
         <f>INDEX(_xll.ACT_COPULA_FRANK_SINGLE(5, 42), 1, 1)</f>
         <v>0.66810646591154232</v>
       </c>
       <c r="C265" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B266">
         <f>_xll.ACT_COPULA_FRANK_CDF(0.5, 0.5, 5)</f>
         <v>0.37714851074652073</v>
       </c>
       <c r="C266" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B269">
         <f>INDEX(_xll.ACT_COPULA_GUMBEL(2, 5, 42), 1, 1)</f>
         <v>0.24161808133885282</v>
       </c>
       <c r="C269" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B270">
         <f>INDEX(_xll.ACT_COPULA_GUMBEL_SINGLE(2, 42), 1, 1)</f>
         <v>0.24161808133885282</v>
       </c>
       <c r="C270" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B271">
         <f>_xll.ACT_COPULA_GUMBEL_CDF(0.5, 0.5, 2)</f>
         <v>0.37521422724648179</v>
       </c>
       <c r="C271" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B274">
         <f>_xll.ACT_COPULA_TAU_TO_THETA(0.5, "CLAYTON")</f>
         <v>2</v>
       </c>
       <c r="C274" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B275">
         <f>_xll.ACT_COPULA_TAIL_LOWER("CLAYTON", 2)</f>
         <v>0.70710678118654757</v>
       </c>
       <c r="C275" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B276">
         <f>_xll.ACT_COPULA_TAIL_UPPER("GUMBEL", 2)</f>
         <v>0.58578643762690485</v>
       </c>
       <c r="C276" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B277">
         <f>_xll.ACT_COPULA_TAIL_LOWER("STUDENT_T", 0.5, 5)</f>
         <v>0.20703125000000355</v>
       </c>
       <c r="C277" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B278">
         <f>_xll.ACT_COPULA_TAIL_UPPER("STUDENT_T", 0.5, 5)</f>
         <v>0.20703125000000355</v>
       </c>
       <c r="C278" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B304" t="str">
         <f>_xll.ACT_VERSION()</f>
         <v>0.7.2</v>
       </c>
       <c r="C304" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B305" t="str">
         <f>_xll.ACT_BUILD_DATE()</f>
         <v>2026-05-04</v>
       </c>
       <c r="C305" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B306" t="str">
         <f>_xll.ACT_GITHUB_URL()</f>
         <v>https://github.com/mdevans21/actuarial_add_in</v>
       </c>
       <c r="C306" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B307">
         <f>_xll.ACT_COMMIT_COUNT()</f>
         <v>14</v>
       </c>
       <c r="C307" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B308" t="str">
         <f>_xll.ACT_COMMIT_INFO(1, "hash")</f>
         <v>v0.7.2</v>
       </c>
       <c r="C308" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B309" t="str">
         <f>_xll.ACT_COMMIT_INFO(1, "date")</f>
         <v>2026-05-04</v>
       </c>
       <c r="C309" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B310" t="str">
         <f>_xll.ACT_COMMIT_INFO(1, "message")</f>
         <v>Workbook polish + Experimental retagging. Mack-SE reference column corrected; Cat Modeling EP-curve table populated; Latest Cumulative restored as a formula; Copulas sheet gains Gaussian/Clayton/Frank/Gumbel sections; Interpolation chart shows interpolated overlay; all charts switched from smooth to straight lines; array formulas promoted via Formula2 to spill correctly. `Actuarial.Aggregate`/`Reinsurance` cat-modelling and return-period functions retagged Experimental to match Copulas/Bootstrap.</v>
       </c>
       <c r="C310" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B311" t="str">
         <f>INDEX(_xll.ACT_COMMIT_HISTORY(), 1, 1)</f>
         <v>Commit</v>
       </c>
       <c r="C311" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B314" cm="1">
         <f t="array" ref="B314:L314">_xll.ACT_DISCRETIZE_EXPONENTIAL(1, 0.5, 10)</f>
@@ -18859,7 +18893,7 @@
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B315" cm="1">
         <f t="array" ref="B315:L315">_xll.ACT_DISCRETIZE_GAMMA(2, 1, 0.5, 10)</f>
@@ -18898,7 +18932,7 @@
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B316" cm="1">
         <f t="array" ref="B316:L316">_xll.ACT_DISCRETIZE_LOGNORMAL(0, 1, 0.5, 10)</f>
@@ -18937,7 +18971,7 @@
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B318" cm="1">
         <f t="array" ref="B318:G318">_xll.ACT_PANJER_POISSON(2, {0.5,0.5}, 5)</f>
@@ -18961,7 +18995,7 @@
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B319" cm="1">
         <f t="array" ref="B319:G319">_xll.ACT_PANJER_NEGBIN(2, 0.5, {0.5,0.5}, 5)</f>
@@ -18985,7 +19019,7 @@
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B320" cm="1">
         <f t="array" ref="B320:G320">_xll.ACT_PANJER_BINOMIAL(5, 0.3, {0.5,0.5}, 5)</f>
@@ -19009,7 +19043,7 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B322" cm="1">
         <f t="array" ref="B322">_xll.ACT_AGGREGATE_MEAN(_xll.ACT_PANJER_POISSON(2, {0.5,0.5}, 5), 1)</f>
@@ -19018,7 +19052,7 @@
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B323" cm="1">
         <f t="array" ref="B323">_xll.ACT_AGGREGATE_STDEV(_xll.ACT_PANJER_POISSON(2, {0.5,0.5}, 5), 1)</f>
@@ -19027,7 +19061,7 @@
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B324" cm="1">
         <f t="array" ref="B324">_xll.ACT_AGGREGATE_VAR_STAT(_xll.ACT_PANJER_POISSON(2, {0.5,0.5}, 5), 1)</f>
@@ -19036,7 +19070,7 @@
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B325" cm="1">
         <f t="array" ref="B325">_xll.ACT_AGGREGATE_CDF(2, _xll.ACT_PANJER_POISSON(2, {0.5,0.5}, 5), 1)</f>
@@ -19045,7 +19079,7 @@
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B326" cm="1">
         <f t="array" ref="B326">_xll.ACT_AGGREGATE_VAR(0.95, _xll.ACT_PANJER_POISSON(2, {0.5,0.5}, 5), 1)</f>
@@ -19054,7 +19088,7 @@
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B327" cm="1">
         <f t="array" ref="B327">_xll.ACT_AGGREGATE_TVAR(0.95, _xll.ACT_PANJER_POISSON(2, {0.5,0.5}, 5), 1)</f>
@@ -19080,31 +19114,31 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -19176,7 +19210,7 @@
         <v>0.5</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -19237,21 +19271,21 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -19337,7 +19371,7 @@
         <v>0.61596065483306206</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -19412,21 +19446,21 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -19599,21 +19633,21 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -19685,7 +19719,7 @@
         <v>0.5</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -19760,21 +19794,21 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -19846,7 +19880,7 @@
         <v>0.59399415029016167</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -19907,21 +19941,21 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -19965,7 +19999,7 @@
         <v>0.63212055882855767</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -20054,21 +20088,21 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -20199,21 +20233,21 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -20372,21 +20406,21 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -20402,7 +20436,7 @@
         <v>0</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -20505,21 +20539,21 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -20650,21 +20684,21 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -20795,21 +20829,21 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -20940,21 +20974,21 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -21026,7 +21060,7 @@
         <v>0.64367062476672832</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
@@ -21087,21 +21121,21 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -21173,7 +21207,7 @@
         <v>0.5</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -21234,21 +21268,21 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="6" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -21320,7 +21354,7 @@
         <v>0.61335546444500655</v>
       </c>
       <c r="D221" s="7" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -21395,7 +21429,7 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B227" s="7">
         <f>_xll.ACT_DIST_ZTPOISSON_MEAN(5)</f>
@@ -21403,26 +21437,26 @@
       </c>
       <c r="C227" s="7"/>
       <c r="D227" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="6" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -21567,7 +21601,7 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="7" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B242" s="7">
         <f>_xll.ACT_DIST_ZTNEGBIN_MEAN(5, 0.3)</f>
@@ -21575,26 +21609,26 @@
       </c>
       <c r="C242" s="7"/>
       <c r="D242" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="6" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -21736,12 +21770,12 @@
         <v>1</v>
       </c>
       <c r="D256" s="7" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B257" s="7">
         <f>_xll.ACT_DIST_ZTBINOM_MEAN(10, 0.3)</f>
@@ -21749,26 +21783,26 @@
       </c>
       <c r="C257" s="7"/>
       <c r="D257" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -21784,7 +21818,7 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="D262" s="7" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -21915,7 +21949,7 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B272" s="7">
         <f>_xll.ACT_DIST_ZTGEOM_MEAN(0.3)</f>
@@ -21923,26 +21957,26 @@
       </c>
       <c r="C272" s="7"/>
       <c r="D272" s="7" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="6" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -21958,7 +21992,7 @@
         <v>0.20539035759926838</v>
       </c>
       <c r="D277" s="7" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -22103,7 +22137,7 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="7" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B288" s="7">
         <f>_xll.ACT_DIST_ZMPOISSON_MEAN(5, 0.2)</f>
@@ -22111,12 +22145,12 @@
       </c>
       <c r="C288" s="7"/>
       <c r="D288" s="7" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="7" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B289" s="7">
         <f>_xll.ACT_DIST_ZMPOISSON_VAR(5, 0.2)</f>
@@ -22124,26 +22158,26 @@
       </c>
       <c r="C289" s="7"/>
       <c r="D289" s="7" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="6" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -22159,7 +22193,7 @@
         <v>0.20194399999999996</v>
       </c>
       <c r="D292" s="7" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -22290,7 +22324,7 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="7" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B302" s="7">
         <f>_xll.ACT_DIST_ZMNEGBIN_MEAN(5, 0.3, 0.2)</f>
@@ -22298,12 +22332,12 @@
       </c>
       <c r="C302" s="7"/>
       <c r="D302" s="7" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="7" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B303" s="7">
         <f>_xll.ACT_DIST_ZMNEGBIN_VAR(5, 0.3, 0.2)</f>
@@ -22314,21 +22348,21 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="6" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -22344,7 +22378,7 @@
         <v>0</v>
       </c>
       <c r="D307" s="7" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -22461,7 +22495,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="7" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B316" s="7">
         <f>_xll.ACT_DIST_PARETO3_MEAN(1, 2, 3)</f>
@@ -22469,26 +22503,26 @@
       </c>
       <c r="C316" s="7"/>
       <c r="D316" s="7" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="6" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -22605,21 +22639,21 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="6" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -22691,7 +22725,7 @@
         <v>0.75589140421441725</v>
       </c>
       <c r="D341" s="7" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -22766,21 +22800,21 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="6" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
@@ -22852,7 +22886,7 @@
         <v>0.63212055882855767</v>
       </c>
       <c r="D356" s="7" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -22927,21 +22961,21 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" s="6" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -23013,7 +23047,7 @@
         <v>0.4</v>
       </c>
       <c r="D371" s="7" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -23105,28 +23139,28 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -23241,27 +23275,27 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -23541,24 +23575,24 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -23794,81 +23828,81 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C49" s="4">
         <f>_xll.ACT_EXPOSURE_POWER(0.5, 2)</f>
         <v>0.25</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C50" s="4">
         <f>_xll.ACT_EXPOSURE_INVERSE_POWER(0.5, 2)</f>
         <v>0.75</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C51" s="4">
         <f>_xll.ACT_EXPOSURE_PARETO(0.5, 2)</f>
         <v>0.29289321881345243</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C52" s="4">
         <f>_xll.ACT_EXPOSURE_RIEBESELL(0.5, 0.5)</f>
         <v>0.85355339059327373</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -23888,28 +23922,28 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -23921,7 +23955,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -23933,7 +23967,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -23945,7 +23979,7 @@
         <v>1000000</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -23957,7 +23991,7 @@
         <v>3000000</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -23969,7 +24003,7 @@
         <v>5000000</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -23981,7 +24015,7 @@
         <v>5000000</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -24002,40 +24036,40 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F4" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -24060,7 +24094,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F7" s="4">
         <v>2</v>
@@ -24083,13 +24117,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -24112,7 +24146,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B9" s="4">
         <v>0.2</v>
@@ -24141,7 +24175,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B10" s="4">
         <v>0.1</v>
@@ -24170,7 +24204,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B11" s="4">
         <v>0.05</v>
@@ -24239,7 +24273,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F14" s="4">
         <v>9</v>
@@ -24262,16 +24296,16 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F15" s="4">
         <v>10</v>
@@ -24335,7 +24369,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -24352,13 +24386,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -24381,7 +24415,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -24496,7 +24530,7 @@
         <v>262.10000000000002</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -24519,7 +24553,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -24565,7 +24599,7 @@
         <v>358.33</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -24588,7 +24622,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -24633,7 +24667,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -24650,13 +24684,13 @@
         <v>0</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -24887,7 +24921,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -38500,15 +38534,15 @@
     </row>
     <row r="1017" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1017" s="6" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="1018" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1018" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B1018" s="3" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="1019" spans="1:4" x14ac:dyDescent="0.25">
@@ -38519,15 +38553,15 @@
     </row>
     <row r="1021" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1021" s="6" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1022" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1022" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B1022" s="3" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="1023" spans="1:4" x14ac:dyDescent="0.25">
@@ -38538,7 +38572,7 @@
     </row>
     <row r="1026" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1026" s="6" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -38559,25 +38593,25 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -38622,21 +38656,21 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -38652,7 +38686,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -38668,7 +38702,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -38684,7 +38718,7 @@
         <v>27.5</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -38700,7 +38734,7 @@
         <v>45</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -38716,7 +38750,7 @@
         <v>67.5</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -38732,7 +38766,7 @@
         <v>92.5</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -38748,12 +38782,12 @@
         <v>105</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -38775,52 +38809,52 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -39085,49 +39119,49 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B21" s="4" cm="1">
         <f t="array" ref="B21">INDEX(_xll.ACT_CL_FACTORS(B7:K16), 1)</f>
@@ -39168,26 +39202,26 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -39362,7 +39396,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B36" s="12">
         <f>SUM(B26:B35)</f>
@@ -39379,18 +39413,18 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -39515,7 +39549,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C50" s="8">
         <v>2447095</v>
@@ -39523,12 +39557,12 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B53" s="4">
         <v>1000</v>
@@ -39536,7 +39570,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B54" s="4">
         <v>42</v>
@@ -39544,23 +39578,23 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B57" s="8">
         <f>INDEX(_xll.ACT_CL_BOOTSTRAP(B7:K16, B53, B54), 1, 2)</f>
@@ -39572,7 +39606,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B58" s="8">
         <f>INDEX(_xll.ACT_CL_BOOTSTRAP(B7:K16, B53, B54), 2, 2)</f>
@@ -39584,7 +39618,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B59" s="8">
         <f>INDEX(_xll.ACT_CL_BOOTSTRAP(B7:K16, B53, B54), 3, 2)</f>
@@ -39593,7 +39627,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B60" s="8">
         <f>INDEX(_xll.ACT_CL_BOOTSTRAP(B7:K16, B53, B54), 4, 2)</f>
@@ -39602,7 +39636,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B61" s="8">
         <f>INDEX(_xll.ACT_CL_BOOTSTRAP(B7:K16, B53, B54), 5, 2)</f>
@@ -39611,7 +39645,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B62" s="8">
         <f>INDEX(_xll.ACT_CL_BOOTSTRAP(B7:K16, B53, B54), 6, 2)</f>
@@ -39620,7 +39654,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B63" s="8">
         <f>INDEX(_xll.ACT_CL_BOOTSTRAP(B7:K16, B53, B54), 7, 2)</f>
@@ -39629,7 +39663,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B64" s="8">
         <f>INDEX(_xll.ACT_CL_BOOTSTRAP(B7:K16, B53, B54), 8, 2)</f>
@@ -39638,7 +39672,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B65" s="8">
         <f>INDEX(_xll.ACT_CL_BOOTSTRAP(B7:K16, B53, B54), 9, 2)</f>
@@ -39647,7 +39681,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B66" s="8">
         <f>INDEX(_xll.ACT_CL_BOOTSTRAP(B7:K16, B53, B54), 10, 2)</f>
@@ -39656,7 +39690,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B67" s="8">
         <f>INDEX(_xll.ACT_CL_BOOTSTRAP(B7:K16, B53, B54), 11, 2)</f>
@@ -39665,33 +39699,33 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D70" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>587</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -39710,7 +39744,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F71" s="8">
         <f>INDEX(_xll.ACT_CL_BOOTSTRAP_ORIGIN(B7:K16, B53, B54), 2, 4)</f>
@@ -40015,7 +40049,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D81" s="8">
         <v>2228677</v>
@@ -40040,34 +40074,34 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B7" s="4">
         <v>1</v>
@@ -40083,7 +40117,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B8" s="4">
         <v>0.9</v>
@@ -40098,7 +40132,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B9" s="4">
         <v>0.3</v>
@@ -40112,12 +40146,12 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B12" s="4">
         <v>5</v>
@@ -40125,7 +40159,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B13" s="4">
         <v>100</v>
@@ -40133,7 +40167,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B14" s="4">
         <v>42</v>
@@ -40141,26 +40175,26 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -41865,17 +41899,17 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -41897,7 +41931,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B128" s="4">
         <v>50</v>
@@ -41905,7 +41939,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B129" s="4">
         <v>42</v>
@@ -41913,13 +41947,13 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -42574,12 +42608,12 @@
     </row>
     <row r="184" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B186" s="4">
         <v>2</v>
@@ -42587,7 +42621,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B187" s="4">
         <v>50</v>
@@ -42595,7 +42629,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B188" s="4">
         <v>42</v>
@@ -42603,13 +42637,13 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -43264,12 +43298,12 @@
     </row>
     <row r="243" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B245" s="4">
         <v>5</v>
@@ -43277,7 +43311,7 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B246" s="4">
         <v>50</v>
@@ -43285,7 +43319,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B247" s="4">
         <v>42</v>
@@ -43293,13 +43327,13 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -43954,12 +43988,12 @@
     </row>
     <row r="302" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B304" s="4">
         <v>2</v>
@@ -43967,7 +44001,7 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B305" s="4">
         <v>50</v>
@@ -43975,7 +44009,7 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B306" s="4">
         <v>42</v>
@@ -43983,13 +44017,13 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">

--- a/excel/actuarial_add_in.xlsx
+++ b/excel/actuarial_add_in.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matth\actuarial_dump_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E942EA-C49D-4CD8-B95C-F5B0E861EBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4F6CD6-8394-4F1D-BF47-6E4236B4AD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2188,7 +2188,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-45B8-4BF9-9E81-C415D07AE718}"/>
+              <c16:uniqueId val="{00000000-E0BD-4811-9134-639F430D872D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2402,7 +2402,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7DCD-4479-B62D-9CF771CC3191}"/>
+              <c16:uniqueId val="{00000000-B230-410A-89AA-494432E71D83}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2617,7 +2617,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AC1D-46F4-83C8-8B81DAE90636}"/>
+              <c16:uniqueId val="{00000000-9C02-41DF-82E7-A07DFEB710B3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2832,7 +2832,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-264A-467B-A587-E37FB57A76C5}"/>
+              <c16:uniqueId val="{00000000-AAB4-4FB9-A9E6-CFE88F281A2B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3047,7 +3047,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8ED5-4E12-93CD-6E9D7ACDCEB9}"/>
+              <c16:uniqueId val="{00000000-AA43-4357-81B3-326B7C9FA519}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3262,7 +3262,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-865F-4874-A56D-AC545B990398}"/>
+              <c16:uniqueId val="{00000000-1C22-48D4-8B57-7DC3C462AE9C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3483,7 +3483,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B721-4EB4-B4F5-093155CFB33A}"/>
+              <c16:uniqueId val="{00000000-941E-43CF-B05C-286C25D9A673}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3705,7 +3705,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1BF0-4C94-BEB7-6099BE6ACBD9}"/>
+              <c16:uniqueId val="{00000000-0225-4945-89F6-74375D25044F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3927,7 +3927,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AC99-4A35-9E5C-E84ED9F55408}"/>
+              <c16:uniqueId val="{00000000-F899-49AC-932A-4AC08FCC4887}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4149,7 +4149,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CC66-4D67-91F4-F05E362498F9}"/>
+              <c16:uniqueId val="{00000000-E610-430D-9236-9692E8F6B073}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4377,7 +4377,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7F31-4572-8E9B-3056984E7AAB}"/>
+              <c16:uniqueId val="{00000000-74E9-4CB8-A574-9AE43129D506}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4605,7 +4605,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-164F-45AD-8F96-2A8D16A4A979}"/>
+              <c16:uniqueId val="{00000000-F411-49AC-A0F5-C53EF11E2A95}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4826,7 +4826,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-26E5-41F1-9FBC-0CE042F7B13F}"/>
+              <c16:uniqueId val="{00000000-1903-433D-B8A0-2888B7B982AF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5042,7 +5042,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C7B4-4A06-B8F5-338ED2CE797D}"/>
+              <c16:uniqueId val="{00000000-B129-47F4-A45C-90816530EE5C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5252,7 +5252,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1ED6-47F6-8D7C-002E86B57067}"/>
+              <c16:uniqueId val="{00000000-5DE2-40CE-911B-5F83C65F228A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5474,7 +5474,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B79C-40B6-80B4-E5648F62D56F}"/>
+              <c16:uniqueId val="{00000000-438B-45B4-AA9A-E3EF27B5E84C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5695,7 +5695,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8E80-45F3-8054-8175D5219AAE}"/>
+              <c16:uniqueId val="{00000000-8FBC-4D6B-AAF4-D12552841B10}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5916,7 +5916,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-13F8-4808-8B6C-300499F15886}"/>
+              <c16:uniqueId val="{00000000-9B5E-44DD-B819-01D86529AA39}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6146,7 +6146,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E00B-4201-B22E-862A04058E8B}"/>
+              <c16:uniqueId val="{00000000-8113-470E-BE9F-F977C71D6FDA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6254,7 +6254,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E00B-4201-B22E-862A04058E8B}"/>
+              <c16:uniqueId val="{00000001-8113-470E-BE9F-F977C71D6FDA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6362,7 +6362,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-E00B-4201-B22E-862A04058E8B}"/>
+              <c16:uniqueId val="{00000002-8113-470E-BE9F-F977C71D6FDA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6470,7 +6470,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-E00B-4201-B22E-862A04058E8B}"/>
+              <c16:uniqueId val="{00000003-8113-470E-BE9F-F977C71D6FDA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6578,7 +6578,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-E00B-4201-B22E-862A04058E8B}"/>
+              <c16:uniqueId val="{00000004-8113-470E-BE9F-F977C71D6FDA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6787,7 +6787,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2E9E-4768-856C-AE21EFB80DCD}"/>
+              <c16:uniqueId val="{00000000-0094-44C2-90C3-BB5AF971277F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6878,7 +6878,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2E9E-4768-856C-AE21EFB80DCD}"/>
+              <c16:uniqueId val="{00000001-0094-44C2-90C3-BB5AF971277F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7109,7 +7109,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-93C6-4B57-BD0B-A9C012E4057A}"/>
+              <c16:uniqueId val="{00000000-E712-4FF2-9A65-D6EC419C80EA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7338,7 +7338,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8A88-469C-AD60-552EA2C9B11D}"/>
+              <c16:uniqueId val="{00000000-F5A0-4F24-9BCB-EEDB6DA9258A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7442,7 +7442,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8A88-469C-AD60-552EA2C9B11D}"/>
+              <c16:uniqueId val="{00000001-F5A0-4F24-9BCB-EEDB6DA9258A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7681,7 +7681,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F40C-458E-8C6D-43A52CB3A190}"/>
+              <c16:uniqueId val="{00000000-0DDB-4D52-A4CB-E5840C1CB65B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7908,7 +7908,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-896B-4A49-B9A4-537402FFF37A}"/>
+              <c16:uniqueId val="{00000000-6078-4F5C-A0B9-2F09C957609D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8678,7 +8678,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F27E-43F3-AA22-A9DB0B287E0E}"/>
+              <c16:uniqueId val="{00000000-44F0-4E68-9150-D4D7622CFA5C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9148,7 +9148,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3D89-467D-BBAB-CA578F281071}"/>
+              <c16:uniqueId val="{00000000-FE40-4837-B73E-ACFD5C27B0DE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9618,7 +9618,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A7D3-46CA-9E99-04C6A29C3433}"/>
+              <c16:uniqueId val="{00000000-3D2C-450B-8879-24E81AFD7915}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10088,7 +10088,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0DD0-45CE-8398-039FADB9FD4B}"/>
+              <c16:uniqueId val="{00000000-B342-44A3-B1CB-A88D18B535D8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10253,7 +10253,7 @@
                   <c:v>0.42463282830797527</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.35380375198453234</c:v>
+                  <c:v>0.35380375198453229</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.44659383954294735</c:v>
@@ -10355,7 +10355,7 @@
                   <c:v>0.51050373743944277</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.14401509733294562</c:v>
+                  <c:v>0.14401509733294554</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.96172356733895836</c:v>
@@ -10412,7 +10412,7 @@
                   <c:v>0.43659012860129937</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2931304282767539</c:v>
+                  <c:v>0.29313042827675378</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.26771098674491789</c:v>
@@ -10469,7 +10469,7 @@
                   <c:v>0.13870552160293764</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.60361747146042066</c:v>
+                  <c:v>0.60361747146042077</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0.80369712894477241</c:v>
@@ -10514,7 +10514,7 @@
                   <c:v>0.50509787790445482</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>6.1403171916247834E-2</c:v>
+                  <c:v>6.1403171916247806E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0.84179786840587534</c:v>
@@ -10558,7 +10558,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0F6A-45A6-9218-413D9D1A0A93}"/>
+              <c16:uniqueId val="{00000000-786F-4540-B98F-D513A8A6421E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10907,7 +10907,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1DB3-40CC-A3C9-B31F55912BD0}"/>
+              <c16:uniqueId val="{00000000-4891-43A4-8F5C-CB66CA8175C8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11100,7 +11100,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-63AA-4F63-BC80-A127376EC4E7}"/>
+              <c16:uniqueId val="{00000000-BF3C-45D0-9379-17477E3E7D6A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11321,7 +11321,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E939-4DB8-89B7-5754C90DF35A}"/>
+              <c16:uniqueId val="{00000000-15CD-42EC-88D3-A6E8E3FAACD4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11536,7 +11536,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A1F3-4E45-84A6-30D9383984B2}"/>
+              <c16:uniqueId val="{00000000-4854-4029-B95D-02C4713E05F0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11751,7 +11751,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-30E3-4A55-B3DB-ACF3B0F29405}"/>
+              <c16:uniqueId val="{00000000-97AB-456C-BF6A-932C6E90449D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11966,7 +11966,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3F5E-4743-97C5-D6B5309B5293}"/>
+              <c16:uniqueId val="{00000000-14C3-41E2-AF14-1510D9576B98}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12193,7 +12193,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A648-4874-A451-93B7F1517430}"/>
+              <c16:uniqueId val="{00000000-B822-4402-B741-E0B74652C8CF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12403,7 +12403,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7BD9-41A3-9616-7907BC2832C7}"/>
+              <c16:uniqueId val="{00000000-A7CC-4C90-B441-405CAE9AFCD1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -13966,7 +13966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="B3" t="str">
         <f>_xll.ACT_VERSION()</f>
-        <v>0.7.3</v>
+        <v>0.8.0</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="B4" t="str">
         <f>_xll.ACT_BUILD_DATE()</f>
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="B8" t="str">
         <f>_xll.ACT_VERSION()</f>
-        <v>0.7.3</v>
+        <v>0.8.0</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="B9" t="str">
         <f>_xll.ACT_BUILD_DATE()</f>
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="B11">
         <f>_xll.ACT_COMMIT_COUNT()</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="B12" t="str">
         <f>_xll.ACT_COMMIT_INFO(1, "message")</f>
-        <v>Bundles five post-v0.7.2 fixes for the public surface: Cat Modeling SPILL collision (OEP/AEP curves now sit side-by-side with full 1000-row clearance, confused static Example 2 dropped); dump-iteration ordering (post-Formula2 errors now surface in dump JSON instead of silently shipping); Versions tab spills `=ACT_COMMIT_HISTORY()` live from the XLL instead of a stale `git log` snapshot; CHANGELOG.md / CONTRIBUTING.md / docs/DEVELOPING.md pulled out of the public repo (release notes live in this method + GitHub Releases).</v>
+        <v>Multi-target net48 + net8.0-windows. Default release asset (`AddIn64-packed.xll`) now targets .NET Framework 4.8 — preinstalled on every Windows 10 1903+ / Windows 11, so installing the add-in no longer requires a runtime download. A .NET 8 perf variant ships alongside as `AddIn64-packed-net8.xll` for users who install the .NET 8 Desktop Runtime; same C# code, modern JIT and SIMD codegen on heavy stochastic workloads. Root cause of the long-standing v0.5.x .NET 8 hosting failure identified: ExcelDna 1.9.0's host shim formats its own runtimeconfig.json from the `.dna` file's RuntimeVersion attribute, which was set to `v4.0` (causing the host to launch .NET 6 and reject the net8 user assembly). MSBuild XmlPoke target now rewrites it to `v8.0` for the net8 build only.</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -14064,7 +14064,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="str" cm="1">
-        <f t="array" ref="A15:C30">_xll.ACT_COMMIT_HISTORY()</f>
+        <f t="array" ref="A15:C31">_xll.ACT_COMMIT_HISTORY()</f>
         <v>Commit</v>
       </c>
       <c r="B15" t="str">
@@ -14076,166 +14076,177 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
-        <v>v0.7.3</v>
+        <v>v0.8.0</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C16" t="str">
-        <v>Bundles five post-v0.7.2 fixes for the public surface: Cat Modeling SPILL collision (OEP/AEP curves now sit side-by-side with full 1000-row clearance, confused static Example 2 dropped); dump-iteration ordering (post-Formula2 errors now surface in dump JSON instead of silently shipping); Versions tab spills `=ACT_COMMIT_HISTORY()` live from the XLL instead of a stale `git log` snapshot; CHANGELOG.md / CONTRIBUTING.md / docs/DEVELOPING.md pulled out of the public repo (release notes live in this method + GitHub Releases).</v>
+        <v>Multi-target net48 + net8.0-windows. Default release asset (`AddIn64-packed.xll`) now targets .NET Framework 4.8 — preinstalled on every Windows 10 1903+ / Windows 11, so installing the add-in no longer requires a runtime download. A .NET 8 perf variant ships alongside as `AddIn64-packed-net8.xll` for users who install the .NET 8 Desktop Runtime; same C# code, modern JIT and SIMD codegen on heavy stochastic workloads. Root cause of the long-standing v0.5.x .NET 8 hosting failure identified: ExcelDna 1.9.0's host shim formats its own runtimeconfig.json from the `.dna` file's RuntimeVersion attribute, which was set to `v4.0` (causing the host to launch .NET 6 and reject the net8 user assembly). MSBuild XmlPoke target now rewrites it to `v8.0` for the net8 build only.</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
-        <v>v0.7.2</v>
+        <v>v0.7.3</v>
       </c>
       <c r="B17" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C17" t="str">
-        <v>Workbook polish + Experimental retagging. Mack-SE reference column corrected; Cat Modeling EP-curve table populated; Latest Cumulative restored as a formula; Copulas sheet gains Gaussian/Clayton/Frank/Gumbel sections; Interpolation chart shows interpolated overlay; all charts switched from smooth to straight lines; array formulas promoted via Formula2 to spill correctly. `Actuarial.Aggregate`/`Reinsurance` cat-modelling and return-period functions retagged Experimental to match Copulas/Bootstrap.</v>
+        <v>Bundles five post-v0.7.2 fixes for the public surface: Cat Modeling SPILL collision (OEP/AEP curves now sit side-by-side with full 1000-row clearance, confused static Example 2 dropped); dump-iteration ordering (post-Formula2 errors now surface in dump JSON instead of silently shipping); Versions tab spills `=ACT_COMMIT_HISTORY()` live from the XLL instead of a stale `git log` snapshot; CHANGELOG.md / CONTRIBUTING.md / docs/DEVELOPING.md pulled out of the public repo (release notes live in this method + GitHub Releases).</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
-        <v>v0.7.1</v>
+        <v>v0.7.2</v>
       </c>
       <c r="B18" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C18" t="str">
-        <v>Patch: replace `int? seed = null` with `object seed = null` + ResolveSeed helper across 13 stochastic functions. ExcelDna 1.9.0 mis-marshals `int?` parameters from Excel even though direct C# calls work — every cell calling the affected functions returned #VALUE! pre-fix (373 cells in the dump test).</v>
+        <v>Workbook polish + Experimental retagging. Mack-SE reference column corrected; Cat Modeling EP-curve table populated; Latest Cumulative restored as a formula; Copulas sheet gains Gaussian/Clayton/Frank/Gumbel sections; Interpolation chart shows interpolated overlay; all charts switched from smooth to straight lines; array formulas promoted via Formula2 to spill correctly. `Actuarial.Aggregate`/`Reinsurance` cat-modelling and return-period functions retagged Experimental to match Copulas/Bootstrap.</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
-        <v>v0.7.0</v>
+        <v>v0.7.1</v>
       </c>
       <c r="B19" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C19" t="str">
-        <v>Breaking: dropped Cape Cod, triangle-utility, calendar-adjust, weighted-average functions (9 in total). Added Mack factor SE / BF / CL_LATEST formulas to spreadsheet; harness now exercises every C# function (174); notebook reconciles every non-trivial function against scipy/Klugman/Bernegger references.</v>
+        <v>Patch: replace `int? seed = null` with `object seed = null` + ResolveSeed helper across 13 stochastic functions. ExcelDna 1.9.0 mis-marshals `int?` parameters from Excel even though direct C# calls work — every cell calling the affected functions returned #VALUE! pre-fix (373 cells in the dump test).</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
-        <v>v0.6.0</v>
+        <v>v0.7.0</v>
       </c>
       <c r="B20" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C20" t="str">
-        <v>Internal cleanups: split Distributions.cs (1686 lines) and ChainLadder.cs (1510 lines) into focused partial-class files; standardised inline string-error returns to ExcelError.ExcelErrorValue (24 sites); test harness now exits non-zero on assertion failures.</v>
+        <v>Breaking: dropped Cape Cod, triangle-utility, calendar-adjust, weighted-average functions (9 in total). Added Mack factor SE / BF / CL_LATEST formulas to spreadsheet; harness now exercises every C# function (174); notebook reconciles every non-trivial function against scipy/Klugman/Bernegger references.</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
-        <v>v0.5.4</v>
+        <v>v0.6.0</v>
       </c>
       <c r="B21" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C21" t="str">
-        <v>Patch: ACT_EXPOSURE_MBBEFD numerical stability — rewrote without explicit `a` to fix NaN at SwissRe c=5 (b&lt;1, b^g underflow) and a 4th-decimal precision loss at c=3.</v>
+        <v>Internal cleanups: split Distributions.cs (1686 lines) and ChainLadder.cs (1510 lines) into focused partial-class files; standardised inline string-error returns to ExcelError.ExcelErrorValue (24 sites); test harness now exits non-zero on assertion failures.</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
-        <v>v0.5.3</v>
+        <v>v0.5.4</v>
       </c>
       <c r="B22" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C22" t="str">
-        <v>Patch: revert to net6.0-windows — neither ExcelDna 1.9.0 nor 1.10-preview4 reliably hosted .NET 8 in Excel. Keeps int? from 1.9; net6 path is known-good.</v>
+        <v>Patch: ACT_EXPOSURE_MBBEFD numerical stability — rewrote without explicit `a` to fix NaN at SwissRe c=5 (b&lt;1, b^g underflow) and a 4th-decimal precision loss at c=3.</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
-        <v>v0.5.2</v>
+        <v>v0.5.3</v>
       </c>
       <c r="B23" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C23" t="str">
-        <v>Patch: tried ExcelDna.AddIn 1.10-preview4 to fix .NET 8 hosting (didn't work).</v>
+        <v>Patch: revert to net6.0-windows — neither ExcelDna 1.9.0 nor 1.10-preview4 reliably hosted .NET 8 in Excel. Keeps int? from 1.9; net6 path is known-good.</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
-        <v>v0.5.1</v>
+        <v>v0.5.2</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="C24" t="str">
-        <v>Patch: drop legacy RuntimeVersion="v4.0" from .dna manifest (necessary but not sufficient — see v0.5.2).</v>
+        <v>Patch: tried ExcelDna.AddIn 1.10-preview4 to fix .NET 8 hosting (didn't work).</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
-        <v>v0.5.0</v>
+        <v>v0.5.1</v>
       </c>
       <c r="B25" t="str">
         <v>2026-05-03</v>
       </c>
       <c r="C25" t="str">
-        <v>Numerical fixes (LAYER_RATE, ILF_PARETO with xm, SWISSRE→Bernegger, AGGREGATE_TVAR); ExcelDna 1.9 + net8.0-windows; nullable seed; copula error handling.</v>
+        <v>Patch: drop legacy RuntimeVersion="v4.0" from .dna manifest (necessary but not sufficient — see v0.5.2).</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
-        <v>v0.4.0</v>
+        <v>v0.5.0</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C26" t="str">
-        <v>GLM hat matrix bootstrap; Aggregate Claims formula fix; broader disclaimers.</v>
+        <v>Numerical fixes (LAYER_RATE, ILF_PARETO with xm, SWISSRE→Bernegger, AGGREGATE_TVAR); ExcelDna 1.9 + net8.0-windows; nullable seed; copula error handling.</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
-        <v>v0.3.1</v>
+        <v>v0.4.0</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-02-21</v>
+        <v>2026-05-02</v>
       </c>
       <c r="C27" t="str">
-        <v>Aggregate Claims tab; spreadsheet rebuilt as .xlsx with full coverage.</v>
+        <v>GLM hat matrix bootstrap; Aggregate Claims formula fix; broader disclaimers.</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>v0.3.0</v>
+        <v>v0.3.1</v>
       </c>
       <c r="B28" t="str">
         <v>2026-02-21</v>
       </c>
       <c r="C28" t="str">
-        <v>Enhanced ODP Bootstrap (E&amp;V 2002); Cape Cod method; credibility removed.</v>
+        <v>Aggregate Claims tab; spreadsheet rebuilt as .xlsx with full coverage.</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>v0.2.0</v>
+        <v>v0.3.0</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-21</v>
       </c>
       <c r="C29" t="str">
-        <v>Panjer recursion; ZT/ZM distributions; Pareto III/IV; Inverse Gaussian; Loglogistic; cat modelling.</v>
+        <v>Enhanced ODP Bootstrap (E&amp;V 2002); Cape Cod method; credibility removed.</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
+        <v>v0.2.0</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Panjer recursion; ZT/ZM distributions; Pareto III/IV; Inverse Gaussian; Loglogistic; cat modelling.</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="str">
         <v>v0.1.0</v>
       </c>
-      <c r="B30" t="str">
+      <c r="B31" t="str">
         <v>2026-01-31</v>
       </c>
-      <c r="C30" t="str">
+      <c r="C31" t="str">
         <v>Initial tagged release: distributions, LEV, chain ladder, Mack, exposure curves.</v>
       </c>
     </row>
@@ -18607,7 +18618,7 @@
       </c>
       <c r="B304" t="str">
         <f>_xll.ACT_VERSION()</f>
-        <v>0.7.3</v>
+        <v>0.8.0</v>
       </c>
       <c r="C304" t="s">
         <v>350</v>
@@ -18619,7 +18630,7 @@
       </c>
       <c r="B305" t="str">
         <f>_xll.ACT_BUILD_DATE()</f>
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C305" t="s">
         <v>352</v>
@@ -18643,7 +18654,7 @@
       </c>
       <c r="B307">
         <f>_xll.ACT_COMMIT_COUNT()</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C307" t="s">
         <v>356</v>
@@ -18655,7 +18666,7 @@
       </c>
       <c r="B308" t="str">
         <f>_xll.ACT_COMMIT_INFO(1, "hash")</f>
-        <v>v0.7.3</v>
+        <v>v0.8.0</v>
       </c>
       <c r="C308" t="s">
         <v>358</v>
@@ -18667,7 +18678,7 @@
       </c>
       <c r="B309" t="str">
         <f>_xll.ACT_COMMIT_INFO(1, "date")</f>
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C309" t="s">
         <v>359</v>
@@ -18679,7 +18690,7 @@
       </c>
       <c r="B310" t="str">
         <f>_xll.ACT_COMMIT_INFO(1, "message")</f>
-        <v>Bundles five post-v0.7.2 fixes for the public surface: Cat Modeling SPILL collision (OEP/AEP curves now sit side-by-side with full 1000-row clearance, confused static Example 2 dropped); dump-iteration ordering (post-Formula2 errors now surface in dump JSON instead of silently shipping); Versions tab spills `=ACT_COMMIT_HISTORY()` live from the XLL instead of a stale `git log` snapshot; CHANGELOG.md / CONTRIBUTING.md / docs/DEVELOPING.md pulled out of the public repo (release notes live in this method + GitHub Releases).</v>
+        <v>Multi-target net48 + net8.0-windows. Default release asset (`AddIn64-packed.xll`) now targets .NET Framework 4.8 — preinstalled on every Windows 10 1903+ / Windows 11, so installing the add-in no longer requires a runtime download. A .NET 8 perf variant ships alongside as `AddIn64-packed-net8.xll` for users who install the .NET 8 Desktop Runtime; same C# code, modern JIT and SIMD codegen on heavy stochastic workloads. Root cause of the long-standing v0.5.x .NET 8 hosting failure identified: ExcelDna 1.9.0's host shim formats its own runtimeconfig.json from the `.dna` file's RuntimeVersion attribute, which was set to `v4.0` (causing the host to launch .NET 6 and reject the net8 user assembly). MSBuild XmlPoke target now rewrites it to `v8.0` for the net8 build only.</v>
       </c>
       <c r="C310" t="s">
         <v>360</v>
@@ -57588,11 +57599,11 @@
       </c>
       <c r="B312" s="3">
         <f>INDEX(_xll.ACT_COPULA_GUMBEL(B304, B305, B306), 4, 1)</f>
-        <v>0.35380375198453234</v>
+        <v>0.35380375198453229</v>
       </c>
       <c r="C312" s="3">
         <f>INDEX(_xll.ACT_COPULA_GUMBEL(B304, B305, B306), 4, 2)</f>
-        <v>0.2931304282767539</v>
+        <v>0.29313042827675378</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -57839,7 +57850,7 @@
       </c>
       <c r="C331" s="3">
         <f>INDEX(_xll.ACT_COPULA_GUMBEL(B304, B305, B306), 23, 2)</f>
-        <v>0.60361747146042066</v>
+        <v>0.60361747146042077</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -58030,11 +58041,11 @@
       </c>
       <c r="B346" s="3">
         <f>INDEX(_xll.ACT_COPULA_GUMBEL(B304, B305, B306), 38, 1)</f>
-        <v>0.14401509733294562</v>
+        <v>0.14401509733294554</v>
       </c>
       <c r="C346" s="3">
         <f>INDEX(_xll.ACT_COPULA_GUMBEL(B304, B305, B306), 38, 2)</f>
-        <v>6.1403171916247834E-2</v>
+        <v>6.1403171916247806E-2</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
